--- a/Assets/Excel/Weapon.xlsx
+++ b/Assets/Excel/Weapon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19875" windowHeight="6930"/>
+    <workbookView windowWidth="15870" windowHeight="9825"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -40,12 +40,24 @@
     <t>atkValue</t>
   </si>
   <si>
+    <t>unlockStr</t>
+  </si>
+  <si>
+    <t>lockType</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>UnlockType</t>
+  </si>
+  <si>
     <t>标识ID</t>
   </si>
   <si>
@@ -55,22 +67,46 @@
     <t>增加的攻击力数值</t>
   </si>
   <si>
+    <t>解锁条件</t>
+  </si>
+  <si>
+    <t>解锁类型</t>
+  </si>
+  <si>
+    <t>条件值</t>
+  </si>
+  <si>
     <t>镇妖剑</t>
   </si>
   <si>
     <t>星穗锄</t>
   </si>
   <si>
+    <t>账号等级到达5级</t>
+  </si>
+  <si>
     <t>翠玉剑</t>
   </si>
   <si>
+    <t>天赋等级到达15级</t>
+  </si>
+  <si>
     <t>墨竹长枪</t>
   </si>
   <si>
+    <t>天赋等级到达30级</t>
+  </si>
+  <si>
     <t>棱月刀</t>
   </si>
   <si>
+    <t>累积使用灵晶达到2000</t>
+  </si>
+  <si>
     <t>星屑剑</t>
+  </si>
+  <si>
+    <t>购买套装获得</t>
   </si>
 </sst>
 </file>
@@ -1004,13 +1040,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="20.875" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1020,93 +1058,171 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
       </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
       </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Weapon.xlsx
+++ b/Assets/Excel/Weapon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15870" windowHeight="9825"/>
+    <workbookView windowWidth="11895" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>attachmentName</t>
+  </si>
+  <si>
+    <t>slotName</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -76,37 +82,64 @@
     <t>条件值</t>
   </si>
   <si>
+    <t>插槽图片字段</t>
+  </si>
+  <si>
+    <t>插槽字段</t>
+  </si>
+  <si>
     <t>镇妖剑</t>
   </si>
   <si>
-    <t>星穗锄</t>
+    <t>箭/1</t>
+  </si>
+  <si>
+    <t>jian</t>
+  </si>
+  <si>
+    <t>星屑剑</t>
   </si>
   <si>
     <t>账号等级到达5级</t>
   </si>
   <si>
+    <t>箭/2</t>
+  </si>
+  <si>
     <t>翠玉剑</t>
   </si>
   <si>
     <t>天赋等级到达15级</t>
   </si>
   <si>
+    <t>箭/3</t>
+  </si>
+  <si>
     <t>墨竹长枪</t>
   </si>
   <si>
     <t>天赋等级到达30级</t>
   </si>
   <si>
+    <t>箭/4</t>
+  </si>
+  <si>
+    <t>星穗剑</t>
+  </si>
+  <si>
+    <t>累积使用灵晶达到2000</t>
+  </si>
+  <si>
+    <t>箭/5</t>
+  </si>
+  <si>
     <t>棱月刀</t>
   </si>
   <si>
-    <t>累积使用灵晶达到2000</t>
-  </si>
-  <si>
-    <t>星屑剑</t>
-  </si>
-  <si>
     <t>购买套装获得</t>
+  </si>
+  <si>
+    <t>箭/6</t>
   </si>
 </sst>
 </file>
@@ -1040,15 +1073,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="16.75" customWidth="1"/>
     <col min="4" max="4" width="20.875" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,53 +1101,71 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1124,19 +1176,25 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1144,19 +1202,25 @@
       <c r="F5">
         <v>5</v>
       </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1164,19 +1228,25 @@
       <c r="F6">
         <v>15</v>
       </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -1184,19 +1254,25 @@
       <c r="F7">
         <v>30</v>
       </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -1204,25 +1280,37 @@
       <c r="F8">
         <v>2000</v>
       </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9">
         <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
